--- a/SB_THROUGH_POINTS.xlsx
+++ b/SB_THROUGH_POINTS.xlsx
@@ -18,17 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -96,19 +92,19 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,7 +188,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -203,7 +198,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Southbound Through — CSAH 61 (Flying Cloud Dr) at College View Dr</a:t>
+              <a:t>Southbound Through  |  CSAH 61 (Flying Cloud Dr) at College View Dr</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -221,14 +216,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="e6194b"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="e6194b"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="e6194b"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -254,14 +259,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="3cb44b"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3cb44b"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="3cb44b"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -287,14 +302,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="4363d8"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4363d8"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4363d8"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -320,14 +345,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="f58231"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="f58231"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="f58231"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -353,14 +388,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="911eb4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="911eb4"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="911eb4"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -386,14 +431,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="42d4f4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="42d4f4"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="42d4f4"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -419,14 +474,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="f032e6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="f032e6"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="f032e6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -452,14 +517,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="a3c832"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="a3c832"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="a3c832"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -485,14 +560,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="f4a8c0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="f4a8c0"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="f4a8c0"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -518,14 +603,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+              <a:solidFill>
+                <a:srgbClr val="469990"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="4"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="469990"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="469990"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -568,8 +663,10 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="100"/>
+        <crossAx val="200"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -577,6 +674,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -595,11 +693,12 @@
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="10"/>
+        <crossAx val="100"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -616,7 +715,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="10080000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -926,7 +1025,7 @@
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -1004,8 +1103,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>0</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>40</v>
@@ -1039,8 +1140,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>1</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
       </c>
       <c r="B4" s="6" t="n">
         <v>17</v>
@@ -1074,8 +1177,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>23</v>
@@ -1109,8 +1214,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>3</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="B6" s="6" t="n">
         <v>15</v>
@@ -1144,8 +1251,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>29</v>
@@ -1179,8 +1288,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>5</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
       </c>
       <c r="B8" s="6" t="n">
         <v>69</v>
@@ -1214,8 +1325,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>168</v>
@@ -1249,8 +1362,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
       </c>
       <c r="B10" s="6" t="n">
         <v>303</v>
@@ -1284,8 +1399,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>8</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>297</v>
@@ -1319,8 +1436,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>9</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
       </c>
       <c r="B12" s="6" t="n">
         <v>269</v>
@@ -1354,8 +1473,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>10</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>331</v>
@@ -1389,8 +1510,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>11</v>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
       </c>
       <c r="B14" s="6" t="n">
         <v>414</v>
@@ -1424,8 +1547,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>12</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>521</v>
@@ -1459,8 +1584,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>13</v>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
       </c>
       <c r="B16" s="6" t="n">
         <v>514</v>
@@ -1494,8 +1621,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>14</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>598</v>
@@ -1529,8 +1658,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>15</v>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
       </c>
       <c r="B18" s="6" t="n">
         <v>732</v>
@@ -1564,8 +1695,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>16</v>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>1292</v>
@@ -1599,8 +1732,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>17</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
       </c>
       <c r="B20" s="6" t="n">
         <v>1284</v>
@@ -1634,8 +1769,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>18</v>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>681</v>
@@ -1669,8 +1806,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>19</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
       </c>
       <c r="B22" s="6" t="n">
         <v>474</v>
@@ -1704,8 +1843,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>20</v>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>351</v>
@@ -1739,8 +1880,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>21</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
       <c r="B24" s="6" t="n">
         <v>246</v>
@@ -1774,8 +1917,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>22</v>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>135</v>

--- a/SB_THROUGH_POINTS.xlsx
+++ b/SB_THROUGH_POINTS.xlsx
@@ -663,10 +663,8 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="200"/>
+        <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -693,7 +691,7 @@
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="100"/>
+        <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>

--- a/SB_THROUGH_POINTS.xlsx
+++ b/SB_THROUGH_POINTS.xlsx
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -108,6 +108,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -645,6 +648,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -671,6 +675,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1020,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1949,6 +1954,43 @@
       </c>
       <c r="K25" s="4" t="n">
         <v>183</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>8803</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>9391</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>9318</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>9064</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>8690</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>8687</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>9780</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>9174</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>9126</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>8642</v>
       </c>
     </row>
   </sheetData>
